--- a/AUSFTA_Declaration_MONAT.xlsx
+++ b/AUSFTA_Declaration_MONAT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalvarez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leudineglobal-my.sharepoint.com/personal/kalvarez_monatglobal_com/Documents/LOGISTIC PAPERWORK GENERATOR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371A099B-F185-42EA-B49A-4160957AD90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{371A099B-F185-42EA-B49A-4160957AD90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC59613-58A2-422B-99FC-C815A4922F1C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AUSFTA Declaration" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>AUSFTA — DECLARATION</t>
   </si>
@@ -79,13 +79,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>3/13/2026</t>
-  </si>
-  <si>
     <t>Name Printed:</t>
-  </si>
-  <si>
-    <t>KEVIN ALVAREZ</t>
   </si>
   <si>
     <t>Company Name:</t>
@@ -391,94 +385,93 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -931,260 +924,273 @@
     <row r="1" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="35"/>
+      <c r="D6" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:8" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="36"/>
+      <c r="D7" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="9" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="33"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="14"/>
     </row>
     <row r="15" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="9" t="s">
+      <c r="A16" s="1"/>
+      <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="9" t="s">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="1"/>
+      <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="9" t="s">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="14"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19" t="s">
+      <c r="B25" s="34"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="21"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="20"/>
     </row>
     <row r="26" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="26" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+    </row>
+    <row r="28" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-    </row>
-    <row r="28" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+    </row>
+    <row r="29" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="27" t="s">
+      <c r="B29" s="25"/>
+      <c r="C29" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-    </row>
-    <row r="29" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+    </row>
+    <row r="31" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-    </row>
-    <row r="31" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="11"/>
+      <c r="B31" s="5"/>
       <c r="C31" s="26"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D11:H11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="D13:H13"/>
@@ -1196,23 +1202,6 @@
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="E25:H25"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="A25:C25"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
